--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,256 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129342318</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92873</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561351</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6628122</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129343531</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>561384</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6628129</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -796,57 +796,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129342318</v>
+        <v>129343531</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561351</v>
+        <v>561384</v>
       </c>
       <c r="R3" t="n">
-        <v>6628122</v>
+        <v>6628129</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +888,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,60 +925,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129343531</v>
+        <v>129342318</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561384</v>
+        <v>561351</v>
       </c>
       <c r="R4" t="n">
-        <v>6628129</v>
+        <v>6628122</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>129342318</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -796,60 +796,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129343531</v>
+        <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561384</v>
+        <v>561351</v>
       </c>
       <c r="R3" t="n">
-        <v>6628129</v>
+        <v>6628122</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,12 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,57 +917,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129342318</v>
+        <v>129343531</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561351</v>
+        <v>561384</v>
       </c>
       <c r="R4" t="n">
-        <v>6628122</v>
+        <v>6628129</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -796,57 +796,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129342318</v>
+        <v>129343531</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561351</v>
+        <v>561384</v>
       </c>
       <c r="R3" t="n">
-        <v>6628122</v>
+        <v>6628129</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +888,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,60 +925,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129343531</v>
+        <v>129342318</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561384</v>
+        <v>561351</v>
       </c>
       <c r="R4" t="n">
-        <v>6628129</v>
+        <v>6628122</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -796,60 +796,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129343531</v>
+        <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561384</v>
+        <v>561351</v>
       </c>
       <c r="R3" t="n">
-        <v>6628129</v>
+        <v>6628122</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,12 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,57 +917,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129342318</v>
+        <v>129343531</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561351</v>
+        <v>561384</v>
       </c>
       <c r="R4" t="n">
-        <v>6628122</v>
+        <v>6628129</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129343531</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129343531</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129343531</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129342318</v>
       </c>
       <c r="B3" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123526751</v>
+        <v>129342318</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Salsmossen N, Vstm</t>
+          <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561333</v>
+        <v>561351</v>
       </c>
       <c r="R2" t="n">
-        <v>6628186</v>
+        <v>6628122</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,82 +776,80 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Tall</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129342318</v>
+        <v>129343531</v>
       </c>
       <c r="B3" t="n">
-        <v>92913</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561351</v>
+        <v>561384</v>
       </c>
       <c r="R3" t="n">
-        <v>6628122</v>
+        <v>6628129</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +888,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129343531</v>
+        <v>123526751</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,49 +936,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen N  om Salsmossen, Ramnäs, Vstm, Skogen N  om Salsmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmossen N, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561384</v>
+        <v>561333</v>
       </c>
       <c r="R4" t="n">
-        <v>6628129</v>
+        <v>6628186</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,27 +999,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Tjädern har suttit på den omkullfallna granlågan.</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,20 +1016,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39694-2025 artfynd.xlsx
+++ b/artfynd/A 39694-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129342318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129343531</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,8 +1053,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>